--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Rafael Uribe Uribe.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Rafael Uribe Uribe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{845840DD-E848-4CFD-86F3-7501D973A608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5D28BB-6577-9444-9C49-22693E7C70EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B7904D7C-25A2-448D-9090-420DA06CBF62}"/>
+    <workbookView xWindow="-120" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{B7904D7C-25A2-448D-9090-420DA06CBF62}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,11 +154,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -250,10 +260,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,12 +275,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -584,9 +604,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3DC469-A949-4B49-8397-95891AABF781}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="5"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="56" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,73 +677,76 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:22" ht="208" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="5">
-        <v>5</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="M2" s="4">
+        <v>3</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="5">
-        <v>5</v>
-      </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="4">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="5">
-        <v>5</v>
-      </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="4">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="5">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="4">
+        <v>3</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="5">
-        <v>5</v>
-      </c>
-      <c r="V2" s="5"/>
+      <c r="U2" s="4">
+        <v>3</v>
+      </c>
+      <c r="V2" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{511A66C1-41DB-2147-B2B9-1041BA79E4DD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Rafael Uribe Uribe.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Rafael Uribe Uribe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5D28BB-6577-9444-9C49-22693E7C70EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49D5DD9-9266-2541-893E-8AB6E416F517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{B7904D7C-25A2-448D-9090-420DA06CBF62}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{B7904D7C-25A2-448D-9090-420DA06CBF62}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -715,31 +715,31 @@
         <v>32</v>
       </c>
       <c r="M2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>33</v>
       </c>
       <c r="O2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>34</v>
       </c>
       <c r="Q2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="S2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>36</v>
       </c>
       <c r="U2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V2" s="4"/>
     </row>
